--- a/r_test/nbclust_analysis/FRST_AK_2_pc_selection_most_frequent_number.xlsx
+++ b/r_test/nbclust_analysis/FRST_AK_2_pc_selection_most_frequent_number.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
   <si>
     <t xml:space="preserve">index</t>
   </si>
@@ -45,6 +45,24 @@
   </si>
   <si>
     <t xml:space="preserve">sdindex</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sdbw</t>
+  </si>
+  <si>
+    <t xml:space="preserve">scott</t>
+  </si>
+  <si>
+    <t xml:space="preserve">marriot</t>
+  </si>
+  <si>
+    <t xml:space="preserve">trcovw</t>
+  </si>
+  <si>
+    <t xml:space="preserve">duda</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pseudot2</t>
   </si>
 </sst>
 </file>
@@ -453,6 +471,54 @@
         <v>10</v>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" t="s">
+        <v>11</v>
+      </c>
+      <c r="B11" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s">
+        <v>12</v>
+      </c>
+      <c r="B12" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s">
+        <v>13</v>
+      </c>
+      <c r="B13" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s">
+        <v>14</v>
+      </c>
+      <c r="B14" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s">
+        <v>15</v>
+      </c>
+      <c r="B15" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s">
+        <v>16</v>
+      </c>
+      <c r="B16" t="n">
+        <v>3</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
